--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129718732</v>
+        <v>129720364</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457800</v>
+        <v>457928</v>
       </c>
       <c r="R4" t="n">
-        <v>6675330</v>
+        <v>6675282</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129720364</v>
+        <v>129718732</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457928</v>
+        <v>457800</v>
       </c>
       <c r="R5" t="n">
-        <v>6675282</v>
+        <v>6675330</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1127,7 +1127,7 @@
         <v>129718637</v>
       </c>
       <c r="B6" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>129720773</v>
       </c>
       <c r="B7" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129718756</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129720204</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129720382</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720333</v>
+        <v>129720424</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457931</v>
+        <v>457932</v>
       </c>
       <c r="R11" t="n">
-        <v>6675282</v>
+        <v>6675320</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720424</v>
+        <v>129720333</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457932</v>
+        <v>457931</v>
       </c>
       <c r="R12" t="n">
-        <v>6675320</v>
+        <v>6675282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1906,7 +1906,7 @@
         <v>129720356</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>129718339</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>129720290</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>129718458</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129733463</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>129733550</v>
       </c>
       <c r="B18" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>129733647</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129733457</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>129733590</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>129733608</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,44 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B2" t="n">
-        <v>91608</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R2" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,53 +787,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>91613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R3" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1244,7 +1244,7 @@
         <v>129720773</v>
       </c>
       <c r="B7" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129718756</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720204</v>
+        <v>129720424</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,37 +1466,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457914</v>
+        <v>457932</v>
       </c>
       <c r="R9" t="n">
-        <v>6675198</v>
+        <v>6675320</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1540,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720382</v>
+        <v>129720333</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,34 +1583,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457939</v>
+        <v>457931</v>
       </c>
       <c r="R10" t="n">
-        <v>6675275</v>
+        <v>6675282</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1657,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720424</v>
+        <v>129720204</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,42 +1700,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457932</v>
+        <v>457914</v>
       </c>
       <c r="R11" t="n">
-        <v>6675320</v>
+        <v>6675198</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,12 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720333</v>
+        <v>129720382</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,39 +1807,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457931</v>
+        <v>457939</v>
       </c>
       <c r="R12" t="n">
-        <v>6675282</v>
+        <v>6675275</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1866,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,12 +1876,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,7 +2023,7 @@
         <v>129718339</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>129718458</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129733463</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,53 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>91613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R2" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +741,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +751,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,44 +778,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B3" t="n">
-        <v>91613</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R3" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720424</v>
+        <v>129720204</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,42 +1466,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457932</v>
+        <v>457914</v>
       </c>
       <c r="R9" t="n">
-        <v>6675320</v>
+        <v>6675198</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,12 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720333</v>
+        <v>129720382</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,39 +1573,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457931</v>
+        <v>457939</v>
       </c>
       <c r="R10" t="n">
-        <v>6675282</v>
+        <v>6675275</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1647,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,12 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720204</v>
+        <v>129720424</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,37 +1680,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457914</v>
+        <v>457932</v>
       </c>
       <c r="R11" t="n">
-        <v>6675198</v>
+        <v>6675320</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1754,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720382</v>
+        <v>129720333</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,34 +1797,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457939</v>
+        <v>457931</v>
       </c>
       <c r="R12" t="n">
-        <v>6675275</v>
+        <v>6675282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1876,7 +1871,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,44 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B2" t="n">
-        <v>91613</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R2" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,53 +787,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>91613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R3" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720204</v>
+        <v>129720382</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457914</v>
+        <v>457939</v>
       </c>
       <c r="R9" t="n">
-        <v>6675198</v>
+        <v>6675275</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720382</v>
+        <v>129720204</v>
       </c>
       <c r="B10" t="n">
         <v>79081</v>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457939</v>
+        <v>457914</v>
       </c>
       <c r="R10" t="n">
-        <v>6675275</v>
+        <v>6675198</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720424</v>
+        <v>129720333</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457932</v>
+        <v>457931</v>
       </c>
       <c r="R11" t="n">
-        <v>6675320</v>
+        <v>6675282</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720333</v>
+        <v>129720424</v>
       </c>
       <c r="B12" t="n">
         <v>57736</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457931</v>
+        <v>457932</v>
       </c>
       <c r="R12" t="n">
-        <v>6675282</v>
+        <v>6675320</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,53 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>91613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R2" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +741,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +751,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,44 +778,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B3" t="n">
-        <v>91613</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R3" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720382</v>
+        <v>129720204</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457939</v>
+        <v>457914</v>
       </c>
       <c r="R9" t="n">
-        <v>6675275</v>
+        <v>6675198</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720204</v>
+        <v>129720382</v>
       </c>
       <c r="B10" t="n">
         <v>79081</v>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457914</v>
+        <v>457939</v>
       </c>
       <c r="R10" t="n">
-        <v>6675198</v>
+        <v>6675275</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720333</v>
+        <v>129720424</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457931</v>
+        <v>457932</v>
       </c>
       <c r="R11" t="n">
-        <v>6675282</v>
+        <v>6675320</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720424</v>
+        <v>129720333</v>
       </c>
       <c r="B12" t="n">
         <v>57736</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457932</v>
+        <v>457931</v>
       </c>
       <c r="R12" t="n">
-        <v>6675320</v>
+        <v>6675282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,44 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B2" t="n">
-        <v>91613</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R2" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,53 +787,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>91617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R3" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129720364</v>
+        <v>129718732</v>
       </c>
       <c r="B4" t="n">
         <v>57736</v>
@@ -921,7 +921,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457928</v>
+        <v>457800</v>
       </c>
       <c r="R4" t="n">
-        <v>6675282</v>
+        <v>6675330</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129718732</v>
+        <v>129720364</v>
       </c>
       <c r="B5" t="n">
         <v>57736</v>
@@ -1038,7 +1038,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457800</v>
+        <v>457928</v>
       </c>
       <c r="R5" t="n">
-        <v>6675330</v>
+        <v>6675282</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720424</v>
+        <v>129720333</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457932</v>
+        <v>457931</v>
       </c>
       <c r="R11" t="n">
-        <v>6675320</v>
+        <v>6675282</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720333</v>
+        <v>129720424</v>
       </c>
       <c r="B12" t="n">
         <v>57736</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457931</v>
+        <v>457932</v>
       </c>
       <c r="R12" t="n">
-        <v>6675282</v>
+        <v>6675320</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129720740</v>
       </c>
       <c r="B3" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129718732</v>
+        <v>129720364</v>
       </c>
       <c r="B4" t="n">
         <v>57736</v>
@@ -921,7 +921,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457800</v>
+        <v>457928</v>
       </c>
       <c r="R4" t="n">
-        <v>6675330</v>
+        <v>6675282</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129720364</v>
+        <v>129718732</v>
       </c>
       <c r="B5" t="n">
         <v>57736</v>
@@ -1038,7 +1038,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457928</v>
+        <v>457800</v>
       </c>
       <c r="R5" t="n">
-        <v>6675282</v>
+        <v>6675330</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720382</v>
+        <v>129720424</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,34 +1573,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457939</v>
+        <v>457932</v>
       </c>
       <c r="R10" t="n">
-        <v>6675275</v>
+        <v>6675320</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1647,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720424</v>
+        <v>129720382</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,39 +1807,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457932</v>
+        <v>457939</v>
       </c>
       <c r="R12" t="n">
-        <v>6675320</v>
+        <v>6675275</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1866,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,12 +1876,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,53 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>91619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R2" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +741,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +751,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,44 +778,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B3" t="n">
-        <v>91619</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R3" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720424</v>
+        <v>129720382</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,39 +1573,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457932</v>
+        <v>457939</v>
       </c>
       <c r="R10" t="n">
-        <v>6675320</v>
+        <v>6675275</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,12 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720333</v>
+        <v>129720424</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1719,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457931</v>
+        <v>457932</v>
       </c>
       <c r="R11" t="n">
-        <v>6675282</v>
+        <v>6675320</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1754,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1764,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1796,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720382</v>
+        <v>129720333</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,34 +1797,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457939</v>
+        <v>457931</v>
       </c>
       <c r="R12" t="n">
-        <v>6675275</v>
+        <v>6675282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1876,7 +1871,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,44 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B2" t="n">
-        <v>91619</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R2" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,53 +787,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>91619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R3" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -675,53 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129719234</v>
+        <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>91619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457852</v>
+        <v>457694</v>
       </c>
       <c r="R2" t="n">
-        <v>6675075</v>
+        <v>6675436</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +741,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +751,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,44 +778,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129720740</v>
+        <v>129719234</v>
       </c>
       <c r="B3" t="n">
-        <v>91619</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457694</v>
+        <v>457852</v>
       </c>
       <c r="R3" t="n">
-        <v>6675436</v>
+        <v>6675075</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129720364</v>
+        <v>129718732</v>
       </c>
       <c r="B4" t="n">
         <v>57736</v>
@@ -921,7 +921,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457928</v>
+        <v>457800</v>
       </c>
       <c r="R4" t="n">
-        <v>6675282</v>
+        <v>6675330</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129718732</v>
+        <v>129720364</v>
       </c>
       <c r="B5" t="n">
         <v>57736</v>
@@ -1038,7 +1038,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457800</v>
+        <v>457928</v>
       </c>
       <c r="R5" t="n">
-        <v>6675330</v>
+        <v>6675282</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720204</v>
+        <v>129720424</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,37 +1466,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457914</v>
+        <v>457932</v>
       </c>
       <c r="R9" t="n">
-        <v>6675198</v>
+        <v>6675320</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1540,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720382</v>
+        <v>129720333</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,34 +1583,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457939</v>
+        <v>457931</v>
       </c>
       <c r="R10" t="n">
-        <v>6675275</v>
+        <v>6675282</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1657,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720424</v>
+        <v>129720204</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,42 +1700,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457932</v>
+        <v>457914</v>
       </c>
       <c r="R11" t="n">
-        <v>6675320</v>
+        <v>6675198</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,12 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720333</v>
+        <v>129720382</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,39 +1807,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457931</v>
+        <v>457939</v>
       </c>
       <c r="R12" t="n">
-        <v>6675282</v>
+        <v>6675275</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1866,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,12 +1876,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2354,7 +2354,7 @@
         <v>129733463</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>129733550</v>
       </c>
       <c r="B18" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>129733647</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129733457</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>129733590</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>129733608</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129718732</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129720364</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129718637</v>
       </c>
       <c r="B6" t="n">
-        <v>56929</v>
+        <v>56930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>129720773</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129718756</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720424</v>
+        <v>129720204</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,42 +1466,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457932</v>
+        <v>457914</v>
       </c>
       <c r="R9" t="n">
-        <v>6675320</v>
+        <v>6675198</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,12 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720333</v>
+        <v>129720382</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,39 +1573,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457931</v>
+        <v>457939</v>
       </c>
       <c r="R10" t="n">
-        <v>6675282</v>
+        <v>6675275</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1647,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,12 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720204</v>
+        <v>129720333</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,37 +1680,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457914</v>
+        <v>457931</v>
       </c>
       <c r="R11" t="n">
-        <v>6675198</v>
+        <v>6675282</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1754,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720382</v>
+        <v>129720424</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,34 +1797,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457939</v>
+        <v>457932</v>
       </c>
       <c r="R12" t="n">
-        <v>6675275</v>
+        <v>6675320</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1876,7 +1871,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,7 +1906,7 @@
         <v>129720356</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>129718339</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>129720290</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>129718458</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>129719234</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129718732</v>
+        <v>129720364</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457800</v>
+        <v>457928</v>
       </c>
       <c r="R4" t="n">
-        <v>6675330</v>
+        <v>6675282</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129720364</v>
+        <v>129718732</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457928</v>
+        <v>457800</v>
       </c>
       <c r="R5" t="n">
-        <v>6675282</v>
+        <v>6675330</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1127,7 +1127,7 @@
         <v>129718637</v>
       </c>
       <c r="B6" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>129720773</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129718756</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129720204</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129720382</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>129720333</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>129720424</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>129720356</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>129718339</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>129720290</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>129718458</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129733463</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>129733550</v>
       </c>
       <c r="B18" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>129733647</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129733457</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>129733590</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>129733608</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>129720773</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129718756</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>129720204</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129720382</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720333</v>
+        <v>129720424</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457931</v>
+        <v>457932</v>
       </c>
       <c r="R11" t="n">
-        <v>6675282</v>
+        <v>6675320</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720424</v>
+        <v>129720333</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457932</v>
+        <v>457931</v>
       </c>
       <c r="R12" t="n">
-        <v>6675320</v>
+        <v>6675282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2023,7 +2023,7 @@
         <v>129718339</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>129718458</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129733463</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129720740</v>
       </c>
       <c r="B2" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>129720773</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129718756</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720204</v>
+        <v>129720333</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,37 +1466,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457914</v>
+        <v>457931</v>
       </c>
       <c r="R9" t="n">
-        <v>6675198</v>
+        <v>6675282</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1540,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720382</v>
+        <v>129720204</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457939</v>
+        <v>457914</v>
       </c>
       <c r="R10" t="n">
-        <v>6675275</v>
+        <v>6675198</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720424</v>
+        <v>129720382</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,39 +1690,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457932</v>
+        <v>457939</v>
       </c>
       <c r="R11" t="n">
-        <v>6675320</v>
+        <v>6675275</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,12 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720333</v>
+        <v>129720424</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457931</v>
+        <v>457932</v>
       </c>
       <c r="R12" t="n">
-        <v>6675282</v>
+        <v>6675320</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2023,7 +2023,7 @@
         <v>129718339</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>129718458</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129733463</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49775-2025 artfynd.xlsx
+++ b/artfynd/A 49775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129720740</v>
+        <v>129718339</v>
       </c>
       <c r="B2" t="n">
-        <v>91648</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457694</v>
+        <v>457706</v>
       </c>
       <c r="R2" t="n">
-        <v>6675436</v>
+        <v>6675354</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129719234</v>
+        <v>129718458</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457852</v>
+        <v>457732</v>
       </c>
       <c r="R3" t="n">
-        <v>6675075</v>
+        <v>6675448</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,53 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129720364</v>
+        <v>129718756</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457928</v>
+        <v>457805</v>
       </c>
       <c r="R4" t="n">
-        <v>6675282</v>
+        <v>6675331</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,53 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129718732</v>
+        <v>129720204</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457800</v>
+        <v>457914</v>
       </c>
       <c r="R5" t="n">
-        <v>6675330</v>
+        <v>6675198</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,53 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129718637</v>
+        <v>129720382</v>
       </c>
       <c r="B6" t="n">
-        <v>56933</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457790</v>
+        <v>457939</v>
       </c>
       <c r="R6" t="n">
-        <v>6675426</v>
+        <v>6675275</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bubbel i skogen.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,48 +1210,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129720773</v>
+        <v>129733463</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röälven, Röälven, Dlr</t>
+          <t>Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457691</v>
+        <v>457896</v>
       </c>
       <c r="R7" t="n">
-        <v>6675436</v>
+        <v>6675574</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,19 +1278,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129718756</v>
+        <v>129720773</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457805</v>
+        <v>457691</v>
       </c>
       <c r="R8" t="n">
-        <v>6675331</v>
+        <v>6675436</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129720424</v>
+        <v>129718732</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1445,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1495,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457932</v>
+        <v>457800</v>
       </c>
       <c r="R9" t="n">
-        <v>6675320</v>
+        <v>6675330</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1572,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129720333</v>
+        <v>129720290</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457931</v>
+        <v>457952</v>
       </c>
       <c r="R10" t="n">
-        <v>6675282</v>
+        <v>6675267</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1647,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,12 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129720382</v>
+        <v>129720333</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,34 +1659,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457939</v>
+        <v>457931</v>
       </c>
       <c r="R11" t="n">
-        <v>6675275</v>
+        <v>6675282</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1759,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1733,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129720204</v>
+        <v>129720356</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,37 +1776,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457914</v>
+        <v>457929</v>
       </c>
       <c r="R12" t="n">
-        <v>6675198</v>
+        <v>6675280</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1876,7 +1850,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129720356</v>
+        <v>129720364</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,13 +1922,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457929</v>
+        <v>457928</v>
       </c>
       <c r="R13" t="n">
-        <v>6675280</v>
+        <v>6675282</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,7 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2020,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129718339</v>
+        <v>129720424</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,37 +2010,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457706</v>
+        <v>457932</v>
       </c>
       <c r="R14" t="n">
-        <v>6675354</v>
+        <v>6675320</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2084,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2127,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129720290</v>
+        <v>129733457</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,17 +2152,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Röälven, Röälven, Dlr</t>
+          <t>Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457952</v>
+        <v>457827</v>
       </c>
       <c r="R15" t="n">
-        <v>6675267</v>
+        <v>6675531</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,24 +2189,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,22 +2206,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129718458</v>
+        <v>129733590</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,37 +2229,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Röälven, Röälven, Dlr</t>
+          <t>Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457732</v>
+        <v>458025</v>
       </c>
       <c r="R16" t="n">
-        <v>6675448</v>
+        <v>6675357</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,19 +2291,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,22 +2308,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129733463</v>
+        <v>129733608</v>
       </c>
       <c r="B17" t="n">
-        <v>79094</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,34 +2331,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457896</v>
+        <v>457962</v>
       </c>
       <c r="R17" t="n">
-        <v>6675574</v>
+        <v>6675499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129733550</v>
+        <v>129733647</v>
       </c>
       <c r="B18" t="n">
-        <v>56921</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,16 +2433,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2476,24 +2450,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2502,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457985</v>
+        <v>458024</v>
       </c>
       <c r="R18" t="n">
-        <v>6675438</v>
+        <v>6675489</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2564,27 +2524,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129733647</v>
+        <v>129733550</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>57132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2592,10 +2552,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2604,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458024</v>
+        <v>457985</v>
       </c>
       <c r="R19" t="n">
-        <v>6675489</v>
+        <v>6675438</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2666,27 +2640,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129733457</v>
+        <v>129718637</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>57144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2697,19 +2671,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Röälven, Dlr</t>
+          <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457827</v>
+        <v>457790</v>
       </c>
       <c r="R20" t="n">
-        <v>6675531</v>
+        <v>6675426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,9 +2713,24 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bubbel i skogen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,62 +2745,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129733590</v>
+        <v>129719234</v>
       </c>
       <c r="B21" t="n">
-        <v>57740</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röälven, Dlr</t>
+          <t>Röälven, Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458025</v>
+        <v>457852</v>
       </c>
       <c r="R21" t="n">
-        <v>6675357</v>
+        <v>6675075</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2841,9 +2830,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,117 +2857,15 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>129733608</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Röälven, Dlr</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>457962</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6675499</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Säfsnäs</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
